--- a/docs/03_detail_design/メッセージ設計書.xlsx
+++ b/docs/03_detail_design/メッセージ設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kamed\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A60822A-F656-4E92-8D40-62B2AA95E4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_D6B1259CA52236B73C4D445B0034FBA3CAEF87BB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-16335" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="244">
   <si>
     <t>勤怠管理アプリ
 メッセージ設計書</t>
@@ -456,6 +456,54 @@
     <t>MVP時点では案内のみ</t>
   </si>
   <si>
+    <t>MSG019</t>
+  </si>
+  <si>
+    <t>F006</t>
+  </si>
+  <si>
+    <t>外出開始打刻成功時</t>
+  </si>
+  <si>
+    <t>外出開始を記録しました。</t>
+  </si>
+  <si>
+    <t>MSG020</t>
+  </si>
+  <si>
+    <t>外出戻り打刻成功時</t>
+  </si>
+  <si>
+    <t>外出戻りを記録しました。</t>
+  </si>
+  <si>
+    <t>MSG021</t>
+  </si>
+  <si>
+    <t>未出勤状態で外出開始した時</t>
+  </si>
+  <si>
+    <t>出勤前のため外出できません。</t>
+  </si>
+  <si>
+    <t>MSG022</t>
+  </si>
+  <si>
+    <t>外出開始前に外出戻りした時</t>
+  </si>
+  <si>
+    <t>外出開始記録がありません。</t>
+  </si>
+  <si>
+    <t>MSG023</t>
+  </si>
+  <si>
+    <t>外出中に外出開始した時</t>
+  </si>
+  <si>
+    <t>既に外出中です。</t>
+  </si>
+  <si>
     <t>ログメッセージ一覧</t>
   </si>
   <si>
@@ -670,6 +718,48 @@
   </si>
   <si>
     <t>スタックトレースと紐付け</t>
+  </si>
+  <si>
+    <t>LOG017</t>
+  </si>
+  <si>
+    <t>外出開始成功時</t>
+  </si>
+  <si>
+    <t>外出開始打刻を登録しました。</t>
+  </si>
+  <si>
+    <t>userId, targetDate, outingStartAt</t>
+  </si>
+  <si>
+    <t>LOG018</t>
+  </si>
+  <si>
+    <t>外出戻り成功時</t>
+  </si>
+  <si>
+    <t>外出戻り打刻を登録しました。</t>
+  </si>
+  <si>
+    <t>userId, targetDate, outingEndAt</t>
+  </si>
+  <si>
+    <t>LOG019</t>
+  </si>
+  <si>
+    <t>未出勤外出開始時</t>
+  </si>
+  <si>
+    <t>出勤前のため外出開始できませんでした。</t>
+  </si>
+  <si>
+    <t>LOG020</t>
+  </si>
+  <si>
+    <t>外出未開始戻り時</t>
+  </si>
+  <si>
+    <t>外出開始記録なしで外出戻りが実行されました。</t>
   </si>
 </sst>
 </file>
@@ -860,10 +950,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1266,8 +1352,8 @@
     <mergeCell ref="E10:G10"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E14:G14"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1677,7 +1763,7 @@
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
     </row>
-    <row r="4" spans="1:11" ht="32.4">
+    <row r="4" spans="1:11" ht="32.4" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>36</v>
       </c>
@@ -1712,7 +1798,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16.2">
+    <row r="5" spans="1:11" ht="16.2" customHeight="1">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1747,7 +1833,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16.2">
+    <row r="6" spans="1:11" ht="16.2" customHeight="1">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -1782,7 +1868,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="32.4">
+    <row r="7" spans="1:11" ht="32.4" customHeight="1">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -1817,7 +1903,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16.2">
+    <row r="8" spans="1:11" ht="16.2" customHeight="1">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -1852,7 +1938,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="32.4">
+    <row r="9" spans="1:11" ht="32.4" customHeight="1">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -1887,7 +1973,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="16.2">
+    <row r="10" spans="1:11" ht="16.2" customHeight="1">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -1922,7 +2008,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="16.2">
+    <row r="11" spans="1:11" ht="16.2" customHeight="1">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -1957,7 +2043,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="16.2">
+    <row r="12" spans="1:11" ht="16.2" customHeight="1">
       <c r="A12" s="3">
         <v>8</v>
       </c>
@@ -1992,7 +2078,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16.2">
+    <row r="13" spans="1:11" ht="16.2" customHeight="1">
       <c r="A13" s="3">
         <v>9</v>
       </c>
@@ -2027,7 +2113,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16.2">
+    <row r="14" spans="1:11" ht="16.2" customHeight="1">
       <c r="A14" s="3">
         <v>10</v>
       </c>
@@ -2062,7 +2148,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16.2">
+    <row r="15" spans="1:11" ht="16.2" customHeight="1">
       <c r="A15" s="3">
         <v>11</v>
       </c>
@@ -2097,7 +2183,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="16.2">
+    <row r="16" spans="1:11" ht="16.2" customHeight="1">
       <c r="A16" s="3">
         <v>12</v>
       </c>
@@ -2132,7 +2218,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="32.4">
+    <row r="17" spans="1:11" ht="32.4" customHeight="1">
       <c r="A17" s="3">
         <v>13</v>
       </c>
@@ -2167,7 +2253,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="16.2">
+    <row r="18" spans="1:11" ht="16.2" customHeight="1">
       <c r="A18" s="3">
         <v>14</v>
       </c>
@@ -2202,7 +2288,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="16.2">
+    <row r="19" spans="1:11" ht="16.2" customHeight="1">
       <c r="A19" s="3">
         <v>15</v>
       </c>
@@ -2237,7 +2323,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="16.2">
+    <row r="20" spans="1:11" ht="16.2" customHeight="1">
       <c r="A20" s="3">
         <v>16</v>
       </c>
@@ -2272,7 +2358,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="32.4">
+    <row r="21" spans="1:11" ht="32.4" customHeight="1">
       <c r="A21" s="3">
         <v>17</v>
       </c>
@@ -2307,7 +2393,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="32.4">
+    <row r="22" spans="1:11" ht="32.4" customHeight="1">
       <c r="A22" s="3">
         <v>18</v>
       </c>
@@ -2342,11 +2428,181 @@
         <v>141</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="19.95" customHeight="1"/>
-    <row r="24" spans="1:11" ht="19.95" customHeight="1"/>
-    <row r="25" spans="1:11" ht="19.95" customHeight="1"/>
-    <row r="26" spans="1:11" ht="19.95" customHeight="1"/>
-    <row r="27" spans="1:11" ht="19.95" customHeight="1"/>
+    <row r="23" spans="1:11" ht="32.4" customHeight="1">
+      <c r="A23" s="3">
+        <v>19</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="32.4" customHeight="1">
+      <c r="A24" s="3">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="32.4" customHeight="1">
+      <c r="A25" s="3">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="32.4" customHeight="1">
+      <c r="A26" s="3">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="32.4" customHeight="1">
+      <c r="A27" s="3">
+        <v>23</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
     <row r="28" spans="1:11" ht="19.95" customHeight="1"/>
     <row r="29" spans="1:11" ht="19.95" customHeight="1"/>
     <row r="30" spans="1:11" ht="19.95" customHeight="1"/>
@@ -2388,7 +2644,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="12" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -2401,7 +2657,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="13" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -2412,15 +2668,15 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
     </row>
-    <row r="4" spans="1:9" ht="16.2">
+    <row r="4" spans="1:9" ht="16.2" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>39</v>
@@ -2429,27 +2685,27 @@
         <v>40</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="32.4">
+    <row r="5" spans="1:9" ht="32.4" customHeight="1">
       <c r="A5" s="3">
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>49</v>
@@ -2458,27 +2714,27 @@
         <v>50</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="16.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16.2" customHeight="1">
       <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>49</v>
@@ -2487,27 +2743,27 @@
         <v>50</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="32.4">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="32.4" customHeight="1">
       <c r="A7" s="3">
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>49</v>
@@ -2519,24 +2775,24 @@
         <v>61</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="32.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="32.4" customHeight="1">
       <c r="A8" s="3">
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>49</v>
@@ -2545,27 +2801,27 @@
         <v>50</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16.2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="16.2" customHeight="1">
       <c r="A9" s="3">
         <v>5</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>66</v>
@@ -2574,27 +2830,27 @@
         <v>67</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16.2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="16.2" customHeight="1">
       <c r="A10" s="3">
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>66</v>
@@ -2606,24 +2862,24 @@
         <v>70</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="32.4">
+    </row>
+    <row r="11" spans="1:9" ht="32.4" customHeight="1">
       <c r="A11" s="3">
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>66</v>
@@ -2632,27 +2888,27 @@
         <v>67</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="16.2">
+    <row r="12" spans="1:9" ht="16.2" customHeight="1">
       <c r="A12" s="3">
         <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>80</v>
@@ -2664,24 +2920,24 @@
         <v>81</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="32.4">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="32.4" customHeight="1">
       <c r="A13" s="3">
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>80</v>
@@ -2690,27 +2946,27 @@
         <v>67</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="32.4">
+    <row r="14" spans="1:9" ht="32.4" customHeight="1">
       <c r="A14" s="3">
         <v>10</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>88</v>
@@ -2722,24 +2978,24 @@
         <v>89</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="32.4">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="32.4" customHeight="1">
       <c r="A15" s="3">
         <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>88</v>
@@ -2748,27 +3004,27 @@
         <v>67</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="16.2">
+    <row r="16" spans="1:9" ht="16.2" customHeight="1">
       <c r="A16" s="3">
         <v>12</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>95</v>
@@ -2780,24 +3036,24 @@
         <v>96</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="32.4">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="32.4" customHeight="1">
       <c r="A17" s="3">
         <v>13</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>95</v>
@@ -2806,27 +3062,27 @@
         <v>67</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="16.2">
+    <row r="18" spans="1:9" ht="16.2" customHeight="1">
       <c r="A18" s="3">
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>113</v>
@@ -2835,27 +3091,27 @@
         <v>114</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="16.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="16.2" customHeight="1">
       <c r="A19" s="3">
         <v>15</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>113</v>
@@ -2864,27 +3120,27 @@
         <v>114</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="32.4">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="32.4" customHeight="1">
       <c r="A20" s="3">
         <v>16</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>102</v>
@@ -2893,22 +3149,134 @@
         <v>102</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="19.95" customHeight="1"/>
-    <row r="22" spans="1:9" ht="19.95" customHeight="1"/>
-    <row r="23" spans="1:9" ht="19.95" customHeight="1"/>
-    <row r="24" spans="1:9" ht="19.95" customHeight="1"/>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="32.4" customHeight="1">
+      <c r="A21" s="3">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="32.4" customHeight="1">
+      <c r="A22" s="3">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="32.4" customHeight="1">
+      <c r="A23" s="3">
+        <v>19</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="32.4" customHeight="1">
+      <c r="A24" s="3">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
     <row r="25" spans="1:9" ht="19.95" customHeight="1"/>
     <row r="26" spans="1:9" ht="19.95" customHeight="1"/>
     <row r="27" spans="1:9" ht="19.95" customHeight="1"/>
